--- a/duoki_editor/resources/data/blank/商店-记忆-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/商店-记忆-1-blank.xlsx
@@ -82,7 +82,7 @@
     <t>好，请听好！神奇盲盒需要的物品是{words}。现在请你在地图上按照顺序把它们指出来！开始吧！</t>
   </si>
   <si>
-    <t>啊哦，这次记错了哦！不过没关系！我下次再带机器人来给你做盲盒！再见～</t>
+    <t>啊哦，这次记错了哦！不过没关系！我下次再带机器人来给你做盲盒！再见！</t>
   </si>
   <si>
     <t>你太厉害了，全对！机器人的盲盒制作程序启动啦！</t>
@@ -91,7 +91,7 @@
     <t>teddy bear|blocks|robot|pencil|crayon|eraser|cup|puzzle|flashlight|jelly|cake|chips|lollipop|cotton candy|popcorn|water|coffee|milkshake|tea</t>
   </si>
   <si>
-    <t>{user_name}，看！神奇盲盒做好了，客人一定会喜欢的！下次有新奇的商品，我再来找你！</t>
+    <t>{user_name}！看！神奇盲盒做好了，客人一定会喜欢的！下次有新奇的商品，我再来找你！</t>
   </si>
 </sst>
 </file>
